--- a/xetroc.xlsx
+++ b/xetroc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08e9d1d1b3ac9846/Lehre/RO MPT ES/RO/xetroc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08e9d1d1b3ac9846/Lehre/RO/xetroc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1281" documentId="8_{1DFA63E7-D0C4-4296-8A41-B08683187CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A2B17E7-849C-493F-93B9-8F2B3E77B9EC}"/>
+  <xr:revisionPtr revIDLastSave="1298" documentId="8_{1DFA63E7-D0C4-4296-8A41-B08683187CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8012E928-279E-5FF6-AD18-8506EEE500AD}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="15634" xr2:uid="{0C8C6F34-8F7C-4CD6-92D1-3EA217BDBAC0}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{0C8C6F34-8F7C-4CD6-92D1-3EA217BDBAC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -1415,6 +1415,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
